--- a/engineer_forms/013_geotechnical_knowledge_assessment--engineer_forms.xlsx
+++ b/engineer_forms/013_geotechnical_knowledge_assessment--engineer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_skill1',_'label':_'geotechnical_skill1'}</t>
+          <t>geotechnical_skill1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_skill1', 'label': 'geotechnical_skill1'}</t>
+          <t>geotechnical skill1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_skill2',_'label':_'geotechnical_skill2'}</t>
+          <t>geotechnical_skill2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_skill2', 'label': 'geotechnical_skill2'}</t>
+          <t>geotechnical skill2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_skill3',_'label':_'geotechnical_skill3'}</t>
+          <t>geotechnical_skill3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_skill3', 'label': 'geotechnical_skill3'}</t>
+          <t>geotechnical skill3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'technical_skill1',_'label':_'technical_skill1'}</t>
+          <t>technical_skill1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'technical_skill1', 'label': 'technical_skill1'}</t>
+          <t>technical skill1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'technical_skill2',_'label':_'technical_skill2'}</t>
+          <t>technical_skill2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'technical_skill2', 'label': 'technical_skill2'}</t>
+          <t>technical skill2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'technical_skill3',_'label':_'technical_skill3'}</t>
+          <t>technical_skill3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'technical_skill3', 'label': 'technical_skill3'}</t>
+          <t>technical skill3</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_cert1',_'label':_'geotechnical_cert1'}</t>
+          <t>geotechnical_cert1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_cert1', 'label': 'geotechnical_cert1'}</t>
+          <t>geotechnical cert1</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_cert2',_'label':_'geotechnical_cert2'}</t>
+          <t>geotechnical_cert2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_cert2', 'label': 'geotechnical_cert2'}</t>
+          <t>geotechnical cert2</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_cert3',_'label':_'geotechnical_cert3'}</t>
+          <t>geotechnical_cert3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_cert3', 'label': 'geotechnical_cert3'}</t>
+          <t>geotechnical cert3</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_tool1',_'label':_'geotechnical_tool1'}</t>
+          <t>geotechnical_tool1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_tool1', 'label': 'geotechnical_tool1'}</t>
+          <t>geotechnical tool1</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_tool2',_'label':_'geotechnical_tool2'}</t>
+          <t>geotechnical_tool2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_tool2', 'label': 'geotechnical_tool2'}</t>
+          <t>geotechnical tool2</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_tool3',_'label':_'geotechnical_tool3'}</t>
+          <t>geotechnical_tool3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_tool3', 'label': 'geotechnical_tool3'}</t>
+          <t>geotechnical tool3</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_language1',_'label':_'geotechnical_language1'}</t>
+          <t>geotechnical_language1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_language1', 'label': 'geotechnical_language1'}</t>
+          <t>geotechnical language1</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_language2',_'label':_'geotechnical_language2'}</t>
+          <t>geotechnical_language2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_language2', 'label': 'geotechnical_language2'}</t>
+          <t>geotechnical language2</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_language3',_'label':_'geotechnical_language3'}</t>
+          <t>geotechnical_language3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_language3', 'label': 'geotechnical_language3'}</t>
+          <t>geotechnical language3</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_cert4',_'label':_'geotechnical_cert4'}</t>
+          <t>geotechnical_cert4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_cert4', 'label': 'geotechnical_cert4'}</t>
+          <t>geotechnical cert4</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_cert5',_'label':_'geotechnical_cert5'}</t>
+          <t>geotechnical_cert5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_cert5', 'label': 'geotechnical_cert5'}</t>
+          <t>geotechnical cert5</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_cert6',_'label':_'geotechnical_cert6'}</t>
+          <t>geotechnical_cert6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_cert6', 'label': 'geotechnical_cert6'}</t>
+          <t>geotechnical cert6</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_cert7',_'label':_'geotechnical_cert7'}</t>
+          <t>geotechnical_cert7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_cert7', 'label': 'geotechnical_cert7'}</t>
+          <t>geotechnical cert7</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_cert8',_'label':_'geotechnical_cert8'}</t>
+          <t>geotechnical_cert8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_cert8', 'label': 'geotechnical_cert8'}</t>
+          <t>geotechnical cert8</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_cert9',_'label':_'geotechnical_cert9'}</t>
+          <t>geotechnical_cert9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_cert9', 'label': 'geotechnical_cert9'}</t>
+          <t>geotechnical cert9</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'bachelor',_'label':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'bachelor', 'label': 'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'master',_'label':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'master', 'label': 'master'}</t>
+          <t>master</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'doctorate',_'label':_'doctorate'}</t>
+          <t>doctorate</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'doctorate', 'label': 'doctorate'}</t>
+          <t>doctorate</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'institution1',_'label':_'institution1'}</t>
+          <t>institution1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'institution1', 'label': 'institution1'}</t>
+          <t>institution1</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'institution2',_'label':_'institution2'}</t>
+          <t>institution2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'institution2', 'label': 'institution2'}</t>
+          <t>institution2</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'institution3',_'label':_'institution3'}</t>
+          <t>institution3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'institution3', 'label': 'institution3'}</t>
+          <t>institution3</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'area1',_'label':_'area1'}</t>
+          <t>area1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'area1', 'label': 'area1'}</t>
+          <t>area1</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'area2',_'label':_'area2'}</t>
+          <t>area2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'area2', 'label': 'area2'}</t>
+          <t>area2</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'area3',_'label':_'area3'}</t>
+          <t>area3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'area3', 'label': 'area3'}</t>
+          <t>area3</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'achievement1',_'label':_'achievement1'}</t>
+          <t>achievement1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'achievement1', 'label': 'achievement1'}</t>
+          <t>achievement1</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'achievement2',_'label':_'achievement2'}</t>
+          <t>achievement2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'achievement2', 'label': 'achievement2'}</t>
+          <t>achievement2</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'achievement3',_'label':_'achievement3'}</t>
+          <t>achievement3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'achievement3', 'label': 'achievement3'}</t>
+          <t>achievement3</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_rec1',_'label':_'geotechnical_rec1'}</t>
+          <t>geotechnical_rec1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_rec1', 'label': 'geotechnical_rec1'}</t>
+          <t>geotechnical rec1</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_rec2',_'label':_'geotechnical_rec2'}</t>
+          <t>geotechnical_rec2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_rec2', 'label': 'geotechnical_rec2'}</t>
+          <t>geotechnical rec2</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'geotechnical_rec3',_'label':_'geotechnical_rec3'}</t>
+          <t>geotechnical_rec3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'geotechnical_rec3', 'label': 'geotechnical_rec3'}</t>
+          <t>geotechnical rec3</t>
         </is>
       </c>
     </row>
